--- a/public/company_templates/upload_course_template.xlsx
+++ b/public/company_templates/upload_course_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guanl\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guanl\OneDrive\Desktop\AI-LMS-TMS\public\company_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F0A7E9-D1F2-4649-9F9D-3FC939F5891E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181830BC-79F7-4F2D-9891-AD2A60EEFE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2CC55B8A-0348-415D-89BB-D63B7BD988EB}"/>
+    <workbookView xWindow="3636" yWindow="0" windowWidth="13776" windowHeight="12360" xr2:uid="{2CC55B8A-0348-415D-89BB-D63B7BD988EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>Domain</t>
   </si>
@@ -169,6 +169,30 @@
   <si>
     <t xml:space="preserve">LU1: Overview of Information Security Management Systems 
 </t>
+  </si>
+  <si>
+    <t>Schedule ID</t>
+  </si>
+  <si>
+    <t>Lesson Plan Link</t>
+  </si>
+  <si>
+    <t>Learner Guide Link</t>
+  </si>
+  <si>
+    <t>Facilitator Guide Link</t>
+  </si>
+  <si>
+    <t>Trainer Slides Link</t>
+  </si>
+  <si>
+    <t>Assessment Plan Link</t>
+  </si>
+  <si>
+    <t>Practical Performance Assessment Link</t>
+  </si>
+  <si>
+    <t>Written Assessment Link</t>
   </si>
 </sst>
 </file>
@@ -255,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -458,11 +482,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF071A5F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -509,14 +544,17 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FC5B37-8826-4A37-921F-ECE9C1C02974}">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.88671875" customWidth="1"/>
@@ -860,31 +898,33 @@
     <col min="4" max="4" width="10.21875" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
     <col min="6" max="6" width="22.109375" customWidth="1"/>
-    <col min="7" max="7" width="79.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="11" max="11" width="20.21875" customWidth="1"/>
-    <col min="12" max="12" width="20.88671875" customWidth="1"/>
-    <col min="13" max="13" width="15.88671875" customWidth="1"/>
-    <col min="17" max="17" width="18.77734375" customWidth="1"/>
-    <col min="18" max="18" width="17.5546875" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="20" width="21.21875" customWidth="1"/>
-    <col min="21" max="21" width="14.44140625" customWidth="1"/>
-    <col min="22" max="22" width="19.6640625" customWidth="1"/>
-    <col min="23" max="23" width="19.5546875" customWidth="1"/>
-    <col min="24" max="24" width="27.44140625" customWidth="1"/>
-    <col min="25" max="25" width="34.44140625" customWidth="1"/>
-    <col min="26" max="26" width="14.33203125" customWidth="1"/>
-    <col min="27" max="27" width="17.109375" customWidth="1"/>
-    <col min="28" max="28" width="20.44140625" customWidth="1"/>
-    <col min="29" max="29" width="12.6640625" customWidth="1"/>
-    <col min="30" max="30" width="28.6640625" customWidth="1"/>
-    <col min="31" max="31" width="41.109375" customWidth="1"/>
-    <col min="32" max="32" width="34.44140625" customWidth="1"/>
+    <col min="7" max="8" width="79.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.21875" customWidth="1"/>
+    <col min="13" max="13" width="20.88671875" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" customWidth="1"/>
+    <col min="18" max="18" width="18.77734375" customWidth="1"/>
+    <col min="19" max="19" width="17.5546875" customWidth="1"/>
+    <col min="20" max="20" width="21" customWidth="1"/>
+    <col min="21" max="21" width="21.21875" customWidth="1"/>
+    <col min="22" max="27" width="14.44140625" customWidth="1"/>
+    <col min="28" max="28" width="24.33203125" customWidth="1"/>
+    <col min="29" max="29" width="19.5546875" customWidth="1"/>
+    <col min="30" max="30" width="19.6640625" customWidth="1"/>
+    <col min="31" max="31" width="19.5546875" customWidth="1"/>
+    <col min="32" max="32" width="27.44140625" customWidth="1"/>
+    <col min="33" max="33" width="34.44140625" customWidth="1"/>
+    <col min="34" max="34" width="14.33203125" customWidth="1"/>
+    <col min="35" max="35" width="17.109375" customWidth="1"/>
+    <col min="36" max="36" width="20.44140625" customWidth="1"/>
+    <col min="37" max="37" width="12.6640625" customWidth="1"/>
+    <col min="38" max="38" width="28.6640625" customWidth="1"/>
+    <col min="39" max="39" width="41.109375" customWidth="1"/>
+    <col min="40" max="40" width="34.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -907,85 +947,109 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -1007,79 +1071,87 @@
       <c r="G2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="21"/>
+      <c r="I2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="10">
+      <c r="J2" s="10">
         <v>1000</v>
       </c>
-      <c r="J2" s="10">
+      <c r="K2" s="10">
         <v>90</v>
       </c>
-      <c r="K2" s="10">
+      <c r="L2" s="10">
         <v>1090</v>
       </c>
-      <c r="L2" s="11">
+      <c r="M2" s="11">
         <v>590</v>
       </c>
-      <c r="M2" s="11">
+      <c r="N2" s="11">
         <v>390</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="5">
         <v>16</v>
       </c>
-      <c r="O2" s="12">
+      <c r="P2" s="12">
         <v>2</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="Q2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="R2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="V2" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="AE2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="AF2" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="AG2" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AH2" t="s">
         <v>35</v>
       </c>
-      <c r="AA2" s="20" t="b">
+      <c r="AI2" t="b">
         <v>0</v>
       </c>
-      <c r="AB2" s="20">
+      <c r="AJ2">
         <v>0</v>
       </c>
-      <c r="AC2" s="20">
+      <c r="AK2">
         <v>0</v>
       </c>
-      <c r="AD2" s="20">
+      <c r="AL2">
         <v>0</v>
       </c>
-      <c r="AF2" s="21" t="s">
+      <c r="AN2" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="AG2" s="20" t="b">
+      <c r="AO2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1089,6 +1161,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="49f33784-c57a-4121-a20e-b1996b91e80e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F8D3CE2C39C8B4B8E3EE3AEB7C10FE8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3cd9e202d9754e77c3f2140d6b82a3fa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="49f33784-c57a-4121-a20e-b1996b91e80e" xmlns:ns4="35f80b19-10d0-4a2a-8766-c61d9d8e5bde" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc2f3bd69f924a26be65f41e1d79ef5" ns3:_="" ns4:_="">
     <xsd:import namespace="49f33784-c57a-4121-a20e-b1996b91e80e"/>
@@ -1321,14 +1401,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="49f33784-c57a-4121-a20e-b1996b91e80e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1339,6 +1411,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1702D9AB-2B2E-4E1D-8146-49F793218E74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="35f80b19-10d0-4a2a-8766-c61d9d8e5bde"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="49f33784-c57a-4121-a20e-b1996b91e80e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A5FCD6F-677B-4487-8208-28A82C4214C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1357,23 +1446,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1702D9AB-2B2E-4E1D-8146-49F793218E74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="35f80b19-10d0-4a2a-8766-c61d9d8e5bde"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="49f33784-c57a-4121-a20e-b1996b91e80e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9406D95F-6AE9-4638-9E98-05EB35638F77}">
   <ds:schemaRefs>
